--- a/prompt.xlsx
+++ b/prompt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="19">
   <si>
     <t>ID</t>
   </si>
@@ -67,6 +67,12 @@
   </si>
   <si>
     <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), traditional chinese ink painting, house explode, black smoke, &lt;lora:Xiaorenshu_v20:1&gt;</t>
+  </si>
+  <si>
+    <t>000400</t>
+  </si>
+  <si>
+    <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), traditional chinese ink painting,Well -looking grassland,Snow mountain, &lt;lora:realisticVisionV20_v20:1&gt;</t>
   </si>
 </sst>
 </file>
@@ -79,14 +85,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -544,48 +543,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -595,97 +597,94 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1044,8 +1043,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="7"/>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="7"/>
   <cols>
     <col min="6" max="7" width="14.5" customWidth="1"/>
     <col min="8" max="8" width="255.625" customWidth="1"/>
@@ -1153,6 +1152,32 @@
       </c>
       <c r="H4" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>32</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>2578261005</v>
+      </c>
+      <c r="G5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/prompt.xlsx
+++ b/prompt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
   <si>
     <t>ID</t>
   </si>
@@ -73,6 +73,21 @@
   </si>
   <si>
     <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), traditional chinese ink painting,Well -looking grassland,Snow mountain, &lt;lora:realisticVisionV20_v20:1&gt;</t>
+  </si>
+  <si>
+    <t>000500</t>
+  </si>
+  <si>
+    <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), no man, dark forest, midnight, no light,Gray leaves</t>
+  </si>
+  <si>
+    <t>000600</t>
+  </si>
+  <si>
+    <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), dark, in forest, black pig monster, with glasses, long white hair, dirty skin, angry, open mouth, long teeth,hornor</t>
+  </si>
+  <si>
+    <t>,</t>
   </si>
 </sst>
 </file>
@@ -1043,8 +1058,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="7"/>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="7"/>
   <cols>
     <col min="6" max="7" width="14.5" customWidth="1"/>
     <col min="8" max="8" width="255.625" customWidth="1"/>
@@ -1178,6 +1193,63 @@
       </c>
       <c r="H5" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>32</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>2578261005</v>
+      </c>
+      <c r="G6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7">
+        <v>32</v>
+      </c>
+      <c r="E7">
+        <v>7</v>
+      </c>
+      <c r="F7">
+        <v>2578261005</v>
+      </c>
+      <c r="G7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="8:8">
+      <c r="H8" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/prompt.xlsx
+++ b/prompt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="44">
   <si>
     <t>ID</t>
   </si>
@@ -81,13 +81,73 @@
     <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), no man, dark forest, midnight, no light,Gray leaves</t>
   </si>
   <si>
+    <t>000501</t>
+  </si>
+  <si>
+    <t>(worst quality:2), (low quality:2), (normal quality:2), lowres, normal quality</t>
+  </si>
+  <si>
+    <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), human Mashed meat mountain, blooding, dark forest, midnight, no light</t>
+  </si>
+  <si>
     <t>000600</t>
   </si>
   <si>
     <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), dark, in forest, black pig monster, with glasses, long white hair, dirty skin, angry, open mouth, long teeth,hornor</t>
   </si>
   <si>
-    <t>,</t>
+    <t>000601</t>
+  </si>
+  <si>
+    <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), no man,  forest, Gray leaves</t>
+  </si>
+  <si>
+    <t>000700</t>
+  </si>
+  <si>
+    <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), traditional chinese ink painting, cave in mountain, stone door, closed</t>
+  </si>
+  <si>
+    <t>000800</t>
+  </si>
+  <si>
+    <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), traditional chinese ink painting, big house,  door with bell</t>
+  </si>
+  <si>
+    <t>000900</t>
+  </si>
+  <si>
+    <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), traditional chinese ink painting, at night, dinner, human meat,human head,human body,human legs,raw meat,blood, no rice</t>
+  </si>
+  <si>
+    <t>001000</t>
+  </si>
+  <si>
+    <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), sun raise, bbehind mountain, red sum</t>
+  </si>
+  <si>
+    <t>001100</t>
+  </si>
+  <si>
+    <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), flower garden, many colors</t>
+  </si>
+  <si>
+    <t>001200</t>
+  </si>
+  <si>
+    <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), Human farm</t>
+  </si>
+  <si>
+    <t>001300</t>
+  </si>
+  <si>
+    <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), fat man eat pig food near pig, happy</t>
+  </si>
+  <si>
+    <t>001400</t>
+  </si>
+  <si>
+    <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), blue sky, white cloud, trees, rivers, mountains,fly birds</t>
   </si>
 </sst>
 </file>
@@ -1058,10 +1118,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="7"/>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="6" max="7" width="14.5" customWidth="1"/>
+    <col min="6" max="6" width="11.5" customWidth="1"/>
+    <col min="7" max="7" width="14.5" customWidth="1"/>
     <col min="8" max="8" width="255.625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1238,18 +1299,270 @@
         <v>7</v>
       </c>
       <c r="F7">
+        <v>2578261006</v>
+      </c>
+      <c r="G7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>32</v>
+      </c>
+      <c r="E8">
+        <v>7</v>
+      </c>
+      <c r="F8">
         <v>2578261005</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G8" t="s">
         <v>11</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9">
+        <v>32</v>
+      </c>
+      <c r="E9">
+        <v>7</v>
+      </c>
+      <c r="F9">
+        <v>257826100</v>
+      </c>
+      <c r="G9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10">
+        <v>32</v>
+      </c>
+      <c r="E10">
+        <v>7</v>
+      </c>
+      <c r="F10">
+        <v>2578261005</v>
+      </c>
+      <c r="G10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11">
+        <v>32</v>
+      </c>
+      <c r="E11">
+        <v>7</v>
+      </c>
+      <c r="F11">
+        <v>2578261005</v>
+      </c>
+      <c r="G11" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <v>32</v>
+      </c>
+      <c r="E12">
+        <v>7</v>
+      </c>
+      <c r="F12">
+        <v>2578261005</v>
+      </c>
+      <c r="H12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13">
+        <v>32</v>
+      </c>
+      <c r="E13">
+        <v>7</v>
+      </c>
+      <c r="F13">
+        <v>2578261005</v>
+      </c>
+      <c r="G13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14">
+        <v>32</v>
+      </c>
+      <c r="E14">
+        <v>7</v>
+      </c>
+      <c r="F14">
+        <v>2578261005</v>
+      </c>
+      <c r="G14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15">
+        <v>32</v>
+      </c>
+      <c r="E15">
+        <v>7</v>
+      </c>
+      <c r="F15">
+        <v>2578261005</v>
+      </c>
+      <c r="G15" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16">
+        <v>32</v>
+      </c>
+      <c r="E16">
+        <v>7</v>
+      </c>
+      <c r="F16">
+        <v>2578261005</v>
+      </c>
+      <c r="G16" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="8:8">
-      <c r="H8" t="s">
-        <v>23</v>
+      <c r="H16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17">
+        <v>32</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+      <c r="F17">
+        <v>2578261005</v>
+      </c>
+      <c r="G17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/prompt.xlsx
+++ b/prompt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="46">
   <si>
     <t>ID</t>
   </si>
@@ -148,6 +148,12 @@
   </si>
   <si>
     <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), blue sky, white cloud, trees, rivers, mountains,fly birds</t>
+  </si>
+  <si>
+    <t>001500</t>
+  </si>
+  <si>
+    <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), The tornado blows the dust all over the sky, and the sky is dark,and the scorched earth,trees,mountain,rain</t>
   </si>
 </sst>
 </file>
@@ -1118,7 +1124,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="6" max="6" width="11.5" customWidth="1"/>
@@ -1563,6 +1569,32 @@
       </c>
       <c r="H17" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18">
+        <v>32</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+      <c r="F18">
+        <v>2578261005</v>
+      </c>
+      <c r="G18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/prompt.xlsx
+++ b/prompt.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12540"/>
+    <workbookView windowWidth="28800" windowHeight="11940"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
     <t>Prompt</t>
   </si>
   <si>
-    <t>000100</t>
+    <t>bg 000100</t>
   </si>
   <si>
     <t>deliberate_v2.safetensors</t>
@@ -57,31 +57,31 @@
     <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), traditional chinese ink painting,  rain, wind, young man riding bicycle, black coat, tall building, cars, &lt;lora:Xiaorenshu_v20:1&gt;</t>
   </si>
   <si>
-    <t>000200</t>
+    <t>bg 000200</t>
   </si>
   <si>
     <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), traditional chinese ink painting, computer on the desktop, lighting, young man is working, hands on the keyboard, big monitor,  black coat, &lt;lora:Xiaorenshu_v20:1&gt;</t>
   </si>
   <si>
-    <t>000300</t>
+    <t>bg 000300</t>
   </si>
   <si>
     <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), traditional chinese ink painting, house explode, black smoke, &lt;lora:Xiaorenshu_v20:1&gt;</t>
   </si>
   <si>
-    <t>000400</t>
+    <t>bg 000400</t>
   </si>
   <si>
     <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), traditional chinese ink painting,Well -looking grassland,Snow mountain, &lt;lora:realisticVisionV20_v20:1&gt;</t>
   </si>
   <si>
-    <t>000500</t>
+    <t>bg 000500</t>
   </si>
   <si>
     <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), no man, dark forest, midnight, no light,Gray leaves</t>
   </si>
   <si>
-    <t>000501</t>
+    <t>bg 000501</t>
   </si>
   <si>
     <t>(worst quality:2), (low quality:2), (normal quality:2), lowres, normal quality</t>
@@ -90,67 +90,67 @@
     <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), human Mashed meat mountain, blooding, dark forest, midnight, no light</t>
   </si>
   <si>
-    <t>000600</t>
+    <t>bg 000600</t>
   </si>
   <si>
     <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), dark, in forest, black pig monster, with glasses, long white hair, dirty skin, angry, open mouth, long teeth,hornor</t>
   </si>
   <si>
-    <t>000601</t>
+    <t>bg 000601</t>
   </si>
   <si>
     <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), no man,  forest, Gray leaves</t>
   </si>
   <si>
-    <t>000700</t>
+    <t>bg 000700</t>
   </si>
   <si>
     <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), traditional chinese ink painting, cave in mountain, stone door, closed</t>
   </si>
   <si>
-    <t>000800</t>
+    <t>bg 000800</t>
   </si>
   <si>
     <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), traditional chinese ink painting, big house,  door with bell</t>
   </si>
   <si>
-    <t>000900</t>
+    <t>bg 000900</t>
   </si>
   <si>
     <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), traditional chinese ink painting, at night, dinner, human meat,human head,human body,human legs,raw meat,blood, no rice</t>
   </si>
   <si>
-    <t>001000</t>
+    <t>bg 001000</t>
   </si>
   <si>
     <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), sun raise, bbehind mountain, red sum</t>
   </si>
   <si>
-    <t>001100</t>
+    <t>bg 001100</t>
   </si>
   <si>
     <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), flower garden, many colors</t>
   </si>
   <si>
-    <t>001200</t>
+    <t>bg 001200</t>
   </si>
   <si>
     <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), Human farm</t>
   </si>
   <si>
-    <t>001300</t>
+    <t>bg 001300</t>
   </si>
   <si>
     <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), fat man eat pig food near pig, happy</t>
   </si>
   <si>
-    <t>001400</t>
+    <t>bg 001400</t>
   </si>
   <si>
     <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), blue sky, white cloud, trees, rivers, mountains,fly birds</t>
   </si>
   <si>
-    <t>001500</t>
+    <t>bg 001500</t>
   </si>
   <si>
     <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), The tornado blows the dust all over the sky, and the sky is dark,and the scorched earth,trees,mountain,rain</t>
@@ -1127,6 +1127,7 @@
   <dimension ref="A1:H18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
+    <col min="1" max="1" width="10.375" customWidth="1"/>
     <col min="6" max="6" width="11.5" customWidth="1"/>
     <col min="7" max="7" width="14.5" customWidth="1"/>
     <col min="8" max="8" width="255.625" customWidth="1"/>
@@ -1185,7 +1186,7 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3" t="s">
@@ -1211,7 +1212,7 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>15</v>
       </c>
       <c r="B4" t="s">
@@ -1237,7 +1238,7 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>17</v>
       </c>
       <c r="B5" t="s">
@@ -1263,7 +1264,7 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>19</v>
       </c>
       <c r="B6" t="s">
@@ -1289,7 +1290,7 @@
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>21</v>
       </c>
       <c r="B7" t="s">
@@ -1315,7 +1316,7 @@
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>24</v>
       </c>
       <c r="B8" t="s">
@@ -1341,7 +1342,7 @@
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>26</v>
       </c>
       <c r="B9" t="s">
@@ -1367,7 +1368,7 @@
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" t="s">
@@ -1393,7 +1394,7 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>30</v>
       </c>
       <c r="B11" t="s">
@@ -1419,7 +1420,7 @@
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>32</v>
       </c>
       <c r="B12" t="s">
@@ -1442,7 +1443,7 @@
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>34</v>
       </c>
       <c r="B13" t="s">
@@ -1468,7 +1469,7 @@
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>36</v>
       </c>
       <c r="B14" t="s">
@@ -1494,7 +1495,7 @@
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>38</v>
       </c>
       <c r="B15" t="s">
@@ -1520,7 +1521,7 @@
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>40</v>
       </c>
       <c r="B16" t="s">
@@ -1546,7 +1547,7 @@
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>42</v>
       </c>
       <c r="B17" t="s">
@@ -1572,7 +1573,7 @@
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>44</v>
       </c>
       <c r="B18" t="s">

--- a/prompt.xlsx
+++ b/prompt.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11940"/>
+    <workbookView windowWidth="28800" windowHeight="12540"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="bg" sheetId="1" r:id="rId1"/>
+    <sheet name="gui" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="52">
   <si>
     <t>ID</t>
   </si>
@@ -154,6 +154,25 @@
   </si>
   <si>
     <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), The tornado blows the dust all over the sky, and the sky is dark,and the scorched earth,trees,mountain,rain</t>
+  </si>
+  <si>
+    <t>bg 001600</t>
+  </si>
+  <si>
+    <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), Dark and dull damp cave with water dripping from the walls</t>
+  </si>
+  <si>
+    <t>bg 001700</t>
+  </si>
+  <si>
+    <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), dead monkey,blooding &lt;lora:BodHor-V1:1&gt;</t>
+  </si>
+  <si>
+    <t>main_menu</t>
+  </si>
+  <si>
+    <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), The tornado blows the dust all over the sky, and the sky is dark,and the scorched earth,trees,mountain,rain
+&lt;lora:BodHor-V1:1&gt;</t>
   </si>
 </sst>
 </file>
@@ -769,9 +788,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
@@ -1124,7 +1146,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="10.375" customWidth="1"/>
@@ -1160,7 +1182,7 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
@@ -1596,6 +1618,55 @@
       </c>
       <c r="H18" t="s">
         <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19">
+        <v>32</v>
+      </c>
+      <c r="E19">
+        <v>7</v>
+      </c>
+      <c r="F19">
+        <v>2578261005</v>
+      </c>
+      <c r="G19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20">
+        <v>32</v>
+      </c>
+      <c r="E20">
+        <v>7</v>
+      </c>
+      <c r="F20">
+        <v>2578261005</v>
+      </c>
+      <c r="H20" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1608,9 +1679,67 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="10.375" customWidth="1"/>
+    <col min="6" max="6" width="16.5" customWidth="1"/>
+    <col min="8" max="8" width="247.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="27" spans="1:8">
+      <c r="A2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <v>32</v>
+      </c>
+      <c r="E2">
+        <v>7</v>
+      </c>
+      <c r="F2">
+        <v>2578261005</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/prompt.xlsx
+++ b/prompt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="60">
   <si>
     <t>ID</t>
   </si>
@@ -166,6 +166,30 @@
   </si>
   <si>
     <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), dead monkey,blooding &lt;lora:BodHor-V1:1&gt;</t>
+  </si>
+  <si>
+    <t>bg 001800</t>
+  </si>
+  <si>
+    <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), meat ball,blooding &lt;lora:BodHor-V1:1&gt;</t>
+  </si>
+  <si>
+    <t>bg 001900</t>
+  </si>
+  <si>
+    <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), Black muddy swamp, dark and dull, with a lot of dead leaves</t>
+  </si>
+  <si>
+    <t>bg 002000</t>
+  </si>
+  <si>
+    <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), sky, dark clouds, lightning,no ground</t>
+  </si>
+  <si>
+    <t>bg 002100</t>
+  </si>
+  <si>
+    <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), meat soup &lt;lora:BodHor-V1:1&gt;</t>
   </si>
   <si>
     <t>main_menu</t>
@@ -1146,7 +1170,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="10.375" customWidth="1"/>
@@ -1667,6 +1691,107 @@
       </c>
       <c r="H20" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21">
+        <v>32</v>
+      </c>
+      <c r="E21">
+        <v>7</v>
+      </c>
+      <c r="F21">
+        <v>2578261005</v>
+      </c>
+      <c r="H21" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22">
+        <v>32</v>
+      </c>
+      <c r="E22">
+        <v>7</v>
+      </c>
+      <c r="F22">
+        <v>2578261005</v>
+      </c>
+      <c r="G22" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23">
+        <v>32</v>
+      </c>
+      <c r="E23">
+        <v>7</v>
+      </c>
+      <c r="F23">
+        <v>2578261005</v>
+      </c>
+      <c r="G23" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24">
+        <v>32</v>
+      </c>
+      <c r="E24">
+        <v>7</v>
+      </c>
+      <c r="F24">
+        <v>2578261005</v>
+      </c>
+      <c r="G24" t="s">
+        <v>22</v>
+      </c>
+      <c r="H24" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1715,7 +1840,7 @@
     </row>
     <row r="2" ht="27" spans="1:8">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
@@ -1736,7 +1861,7 @@
         <v>11</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/prompt.xlsx
+++ b/prompt.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12540"/>
+    <workbookView windowWidth="28800" windowHeight="12540" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="bg" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="73">
   <si>
     <t>ID</t>
   </si>
@@ -197,6 +197,45 @@
   <si>
     <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), The tornado blows the dust all over the sky, and the sky is dark,and the scorched earth,trees,mountain,rain
 &lt;lora:BodHor-V1:1&gt;</t>
+  </si>
+  <si>
+    <t>suan normal</t>
+  </si>
+  <si>
+    <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), traditional chinese ink painting,  old man,white hair,looking at viewer, full body portrait, &lt;lora:Xiaorenshu_v20:1&gt;</t>
+  </si>
+  <si>
+    <t>pm normal</t>
+  </si>
+  <si>
+    <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), traditional chinese ink painting,  young woman,beauty,looking at viewer, full body portrait, &lt;lora:Xiaorenshu_v20:1&gt;</t>
+  </si>
+  <si>
+    <t>luren normal</t>
+  </si>
+  <si>
+    <t>perfect_world</t>
+  </si>
+  <si>
+    <t xml:space="preserve">masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), traditional chinese ink painting,  old woman,gray hair,looking at viewer, full body portrait </t>
+  </si>
+  <si>
+    <t>laoren normal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), traditional chinese ink painting,  fat man,looking at viewer, full body portrait </t>
+  </si>
+  <si>
+    <t>e normal</t>
+  </si>
+  <si>
+    <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), traditional chinese ink painting,  girl,blonde,beauty,looking at viewer, full body portrait,simile face</t>
+  </si>
+  <si>
+    <t>sun normal</t>
+  </si>
+  <si>
+    <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), traditional chinese ink painting,  Sun Wukong,looking at viewer, full body portrait,angry face,t-shirt</t>
   </si>
 </sst>
 </file>
@@ -1804,10 +1843,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="7"/>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="10.375" customWidth="1"/>
+    <col min="1" max="1" width="13.75" customWidth="1"/>
     <col min="6" max="6" width="16.5" customWidth="1"/>
     <col min="8" max="8" width="247.125" customWidth="1"/>
   </cols>
@@ -1862,6 +1901,162 @@
       </c>
       <c r="H2" s="1" t="s">
         <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>32</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>2578261006</v>
+      </c>
+      <c r="G3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>32</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4">
+        <v>2578261006</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>32</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>2578261006</v>
+      </c>
+      <c r="G5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>32</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>2578261006</v>
+      </c>
+      <c r="G6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7">
+        <v>32</v>
+      </c>
+      <c r="E7">
+        <v>7</v>
+      </c>
+      <c r="F7">
+        <v>2578261006</v>
+      </c>
+      <c r="G7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>32</v>
+      </c>
+      <c r="E8">
+        <v>7</v>
+      </c>
+      <c r="F8">
+        <v>2578261018</v>
+      </c>
+      <c r="G8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/prompt.xlsx
+++ b/prompt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="79">
   <si>
     <t>ID</t>
   </si>
@@ -236,6 +236,25 @@
   </si>
   <si>
     <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), traditional chinese ink painting,  Sun Wukong,looking at viewer, full body portrait,angry face,t-shirt</t>
+  </si>
+  <si>
+    <t>zhu normal</t>
+  </si>
+  <si>
+    <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), traditional chinese ink painting,  fat pig man,looking at viewer, full body portrait,angry face,t-shirt</t>
+  </si>
+  <si>
+    <t>tang normal</t>
+  </si>
+  <si>
+    <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), traditional chinese ink painting, Buddhist man,bald,looking at viewer, full body portrait</t>
+  </si>
+  <si>
+    <t>sha normal</t>
+  </si>
+  <si>
+    <t>masterpiece, sharp focus, 8k, highly detailed, best quality, ultra detailed, ultra high res, (photorealistic:1.5), traditional chinese ink painting, bearded,monster,looking at viewer, full body portrait
+ &lt;lora:BodHor-V1:1&gt;</t>
   </si>
 </sst>
 </file>
@@ -851,9 +870,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1245,7 +1267,7 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
@@ -1843,8 +1865,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="7"/>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="13.75" customWidth="1"/>
     <col min="6" max="6" width="16.5" customWidth="1"/>
@@ -2044,7 +2066,7 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -2057,6 +2079,84 @@
       </c>
       <c r="H8" t="s">
         <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9">
+        <v>32</v>
+      </c>
+      <c r="E9">
+        <v>7</v>
+      </c>
+      <c r="F9">
+        <v>2578261019</v>
+      </c>
+      <c r="G9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10">
+        <v>32</v>
+      </c>
+      <c r="E10">
+        <v>7</v>
+      </c>
+      <c r="F10">
+        <v>2578261005</v>
+      </c>
+      <c r="G10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" ht="27" spans="1:8">
+      <c r="A11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11">
+        <v>32</v>
+      </c>
+      <c r="E11">
+        <v>7</v>
+      </c>
+      <c r="F11">
+        <v>2578261008</v>
+      </c>
+      <c r="G11" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
